--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aysegulkucukoglu/Documents/Rosary Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565B2AEB-91BB-6C4C-9B4F-4829B7BB6073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBE44AD-5805-3049-A3FE-7EE97E9D0A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ürün Kataloğu" sheetId="1" r:id="rId1"/>
@@ -451,7 +451,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1917,11 +1924,11 @@
       <c r="H17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="5">
         <v>3000</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="5"/>
@@ -1970,21 +1977,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{F33B7C9F-4EC9-3B46-B2F4-A55998A4C073}">
-            <xm:f>NOT(ISERROR(SEARCH("-",J1)))</xm:f>
-            <xm:f>"-"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="5" tint="0.59996337778862885"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>J2:K1048576 J1</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{A5B7E675-8585-AB41-A517-427893EDE478}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{A5B7E675-8585-AB41-A517-427893EDE478}">
             <xm:f>NOT(ISERROR(SEARCH("-",I13)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -1997,6 +1990,34 @@
           </x14:cfRule>
           <xm:sqref>I13</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{F33B7C9F-4EC9-3B46-B2F4-A55998A4C073}">
+            <xm:f>NOT(ISERROR(SEARCH("-",J1)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="5" tint="0.59996337778862885"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J1 J2:K16 J18:K1048576 K17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{8F1DD2CD-89CC-7C4B-A96A-36F05EEC4182}">
+            <xm:f>NOT(ISERROR(SEARCH("-",I17)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="5" tint="0.59996337778862885"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>I17</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -777,6 +777,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -802,6 +805,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2077,7 +2083,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>İki renkli değerli taşın yan yana yerleştirildiği bir Toi et Moi yüzük. 14K altın (sarı veya beyaz) ya da 925 gümüş üzeri 14K beyaz altın rodaj olarak üretilebilir.</t>
+          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki farklı taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte iki renkli değerli taş yan yana konumlanır. 14K altın (sarı veya beyaz) ya da 925 gümüş üzeri 14K beyaz altın rodaj olarak üretilebilir.</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -760,13 +760,13 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -788,7 +788,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -805,9 +805,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2043,7 +2040,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Sertifikalı 1 ct ve 3 ct D/E renk lab-grown pırlantalarla üretilen bir Toi et Moi yüzük. Taşlar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak talep edilebilir.</t>
+          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte sertifikalı 1 ct ve 3 ct D/E renk lab-grown pırlantalar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak talep edilebilir.</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -760,7 +760,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -788,7 +788,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -805,6 +805,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2040,12 +2043,12 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte sertifikalı 1 ct ve 3 ct D/E renk lab-grown pırlantalar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak talep edilebilir.</t>
+          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte IGI sertifikalı 1 ct ve 3 ct D/E renk lab-grown pırlantalar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak talep edilebilir.</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Lab-Grown Pırlanta D/E, 1 ct + 3 ct (sertifikalı)</t>
+          <t>IGI Sertifikalı Lab-Grown Pırlanta D/E, 1 ct + 3 ct</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte IGI sertifikalı 1 ct ve 3 ct D/E renk lab-grown pırlantalar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak talep edilebilir.</t>
+          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte IGI sertifikalı 1 ct ve 3 ct D/E renk lab-grown pırlantalar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak sipariş verilebilir.</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -760,7 +760,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -788,7 +788,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -805,9 +805,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -805,6 +805,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2040,12 +2043,12 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte IGI sertifikalı 1 ct ve 3 ct D/E renk lab-grown pırlantalar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak sipariş verilebilir.</t>
+          <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte IGI sertifikalı 0.9 ct ve 2.0 ct D/E renk lab-grown pırlantalar 14K altın montür üzerinde birlikte oturtulmuştur. Sarı veya beyaz altın olarak sipariş verilebilir.</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>IGI Sertifikalı Lab-Grown Pırlanta D/E, 1 ct + 3 ct</t>
+          <t>IGI Sertifikalı Lab-Grown Pırlanta D/E, 0.9 ct (6.30 mm) + 2.0 ct (12.00 × 7.00 mm)</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -1939,7 +1939,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Zirkon Taşlı Altın Kaplama Saç Tokası</t>
+          <t>Zirkon Taşlı Saç Tokası</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1954,13 +1954,11 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>14K Altın / Kaplama</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>925 Gümüş / Gümüş Üzeri Altın Kaplama</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>2000</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>3000</v>

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -736,7 +736,7 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 17" descr="Picture"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -746,12 +746,32 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -770,34 +790,6 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
         <a:blip cstate="print" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
@@ -805,9 +797,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -250,13 +250,13 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -266,12 +266,91 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -286,22 +365,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 2" descr="Picture"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -316,22 +390,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 3" descr="Picture"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -346,22 +415,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 4" descr="Picture"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -376,22 +440,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 5" descr="Picture"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -406,22 +465,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 6" descr="Picture"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -436,22 +490,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 7" descr="Picture"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -466,22 +515,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 8" descr="Picture"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -496,22 +540,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 9" descr="Picture"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -526,22 +565,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 10" descr="Picture"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -556,22 +590,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 11" descr="Picture"/>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -586,22 +615,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 12" descr="Picture"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -616,22 +640,17 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 13" descr="Picture"/>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
+        <a:blip cstate="print" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -641,96 +660,6 @@
       <col>1</col>
       <colOff>0</colOff>
       <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -755,7 +684,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -780,7 +709,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aysegulkucukoglu/Documents/Rosary Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960AA6FC-08B9-6F40-93E1-91A95D7ABC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C3A545-BB5E-A843-B8D9-0DD377952410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -567,12 +567,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2422,167 +2416,155 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12">
+      <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="12">
-        <v>34000</v>
-      </c>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
+      <c r="I21" s="11">
+        <v>32000</v>
+      </c>
+      <c r="J21" s="11"/>
     </row>
     <row r="22" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12">
+      <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I22" s="12">
-        <v>24000</v>
-      </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
+      <c r="I22" s="11">
+        <v>22000</v>
+      </c>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12">
+      <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="12">
-        <v>81000</v>
-      </c>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12">
-        <v>78000</v>
-      </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12" t="s">
+      <c r="I23" s="11">
+        <v>77000</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="4">
+        <v>74000</v>
+      </c>
+      <c r="M23" s="6" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12">
+      <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <v>16000</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="11">
         <v>18000</v>
       </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12" t="s">
+      <c r="M24" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12">
+      <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="11">
         <v>23000</v>
       </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
+      <c r="J25" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rosary-urun-katalogu.xlsx
+++ b/rosary-urun-katalogu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aysegulkucukoglu/Documents/Rosary Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C3A545-BB5E-A843-B8D9-0DD377952410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ACAEFC-A253-8645-9AAB-43A67EEDC8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="135">
   <si>
     <t>No</t>
   </si>
@@ -360,9 +360,6 @@
     <t>Fransızca 'sen ve ben' anlamına gelen Toi et Moi, yan yana yerleştirilen iki farklı taşla iki ruhun bir araya gelişini anlatır; tarih boyunca aşkın, bağlılığın ve eşit ortaklığın simgesi olarak görülmüştür. Bu yüzükte iki renkli değerli taş yan yana konumlanır. 14K altın (sarı veya beyaz) ya da 925 gümüş üzeri 14K beyaz altın rodaj olarak üretilebilir.</t>
   </si>
   <si>
-    <t>Renkli Değerli Taşlar</t>
-  </si>
-  <si>
     <t>14K Altın (Sarı/Beyaz) / 925SS 14K Beyaz Altın Rodaj</t>
   </si>
   <si>
@@ -411,9 +408,6 @@
     <t>Dalga Formlu Üçlü Renkli Doğal Taşlı Yüzük Seti</t>
   </si>
   <si>
-    <t>Renkli Doğal Taşlar (ametist, kuvars, safir, yakut, zümrüt vb.)</t>
-  </si>
-  <si>
     <t>925 Gümüş / 925SS 14K Altın Kaplama (Sarı veya Beyaz)</t>
   </si>
   <si>
@@ -430,6 +424,9 @@
   </si>
   <si>
     <t>Üç dalga formlu yüzüğün, renkli doğal taşlarla süslendiği bir set. Birlikte ya da ayrı ayrı takılabilir; diğer dalga formlu modellerle kombin yapılabilir.</t>
+  </si>
+  <si>
+    <t>Renkli Doğal Taşlar (kuvars)</t>
   </si>
 </sst>
 </file>
@@ -537,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -566,6 +563,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1737,7 +1737,7 @@
     <col min="8" max="8" width="20" style="4" customWidth="1"/>
     <col min="9" max="9" width="18" style="4" customWidth="1"/>
     <col min="10" max="12" width="22" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -2396,23 +2396,23 @@
       <c r="D20" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>110</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>113</v>
-      </c>
       <c r="I20" s="11">
-        <v>46000</v>
+        <v>24000</v>
       </c>
       <c r="J20" s="11">
-        <v>14000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2421,22 +2421,22 @@
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="G21" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="H21" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="I21" s="11">
         <v>32000</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>122</v>
-      </c>
       <c r="H22" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I22" s="11">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="J22" s="11"/>
     </row>
@@ -2477,22 +2477,22 @@
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="F23" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>102</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I23" s="11">
         <v>77000</v>
@@ -2502,7 +2502,7 @@
         <v>74000</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2511,31 +2511,31 @@
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="11" t="s">
+      <c r="I24" s="11">
+        <v>9000</v>
+      </c>
+      <c r="J24" s="11">
+        <v>11000</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="I24" s="11">
-        <v>16000</v>
-      </c>
-      <c r="J24" s="11">
-        <v>18000</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2544,22 +2544,22 @@
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>102</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I25" s="11">
         <v>23000</v>
